--- a/public/plantilla-sustancias-quimicas.xlsx
+++ b/public/plantilla-sustancias-quimicas.xlsx
@@ -549,7 +549,7 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-sustancias-quimicas.xlsx
+++ b/public/plantilla-sustancias-quimicas.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sustancias Químicas" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-sustancias-quimicas.xlsx
+++ b/public/plantilla-sustancias-quimicas.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sustancias Químicas" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+  <numFmts count="0"/>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,6 +139,10 @@
       <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -510,7 +515,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -712,6 +717,48 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2344,6 +2391,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2693,6 +2808,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="33" min="1" max="1"/>
     <col width="13" customWidth="1" style="33" min="2" max="3"/>
+    <col width="13" customWidth="1" style="33" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="33" min="4" max="4"/>
     <col width="10" customWidth="1" style="33" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="33" min="6" max="6"/>
@@ -2859,16 +2975,16 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="C11" s="79" t="n"/>
+      <c r="D11" s="80" t="n"/>
+      <c r="E11" s="80" t="n"/>
+      <c r="F11" s="80" t="n"/>
+      <c r="G11" s="80" t="n"/>
+      <c r="H11" s="80" t="n"/>
+      <c r="I11" s="80" t="n"/>
+      <c r="J11" s="80" t="n"/>
+      <c r="K11" s="80" t="n"/>
+      <c r="L11" s="81" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="33">
       <c r="A12" s="25" t="inlineStr">
@@ -2877,20 +2993,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="79" t="n"/>
+      <c r="D12" s="80" t="n"/>
+      <c r="E12" s="80" t="n"/>
+      <c r="F12" s="80" t="n"/>
+      <c r="G12" s="81" t="n"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="31" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="79" t="n"/>
+      <c r="K12" s="80" t="n"/>
+      <c r="L12" s="81" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="33">
       <c r="A13" s="25" t="inlineStr">
@@ -2899,24 +3015,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="82" t="n"/>
+      <c r="D13" s="81" t="n"/>
       <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Almacén o zona</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="79" t="n"/>
+      <c r="H13" s="81" t="n"/>
       <c r="I13" s="25" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="31" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="79" t="n"/>
+      <c r="L13" s="81" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="33">
       <c r="A14" s="35" t="inlineStr">
@@ -2983,196 +3099,196 @@
       </c>
     </row>
     <row r="16" ht="22.05" customHeight="1" s="33">
-      <c r="A16" s="48" t="n">
+      <c r="A16" s="83" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="46" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="48" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="48" t="n"/>
-      <c r="I16" s="46" t="n"/>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="48" t="n"/>
-      <c r="L16" s="48" t="n"/>
+      <c r="B16" s="84" t="n"/>
+      <c r="C16" s="85" t="n"/>
+      <c r="D16" s="86" t="n"/>
+      <c r="E16" s="87" t="n"/>
+      <c r="F16" s="86" t="n"/>
+      <c r="G16" s="87" t="n"/>
+      <c r="H16" s="87" t="n"/>
+      <c r="I16" s="84" t="n"/>
+      <c r="J16" s="86" t="n"/>
+      <c r="K16" s="87" t="n"/>
+      <c r="L16" s="87" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1" s="33">
-      <c r="A17" s="48" t="n">
+      <c r="A17" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="46" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="48" t="n"/>
-      <c r="I17" s="46" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="48" t="n"/>
-      <c r="L17" s="48" t="n"/>
+      <c r="B17" s="84" t="n"/>
+      <c r="C17" s="85" t="n"/>
+      <c r="D17" s="86" t="n"/>
+      <c r="E17" s="87" t="n"/>
+      <c r="F17" s="86" t="n"/>
+      <c r="G17" s="87" t="n"/>
+      <c r="H17" s="87" t="n"/>
+      <c r="I17" s="84" t="n"/>
+      <c r="J17" s="86" t="n"/>
+      <c r="K17" s="87" t="n"/>
+      <c r="L17" s="87" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1" s="33">
-      <c r="A18" s="48" t="n">
+      <c r="A18" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="48" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="48" t="n"/>
-      <c r="H18" s="48" t="n"/>
-      <c r="I18" s="46" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="48" t="n"/>
-      <c r="L18" s="48" t="n"/>
+      <c r="B18" s="84" t="n"/>
+      <c r="C18" s="85" t="n"/>
+      <c r="D18" s="86" t="n"/>
+      <c r="E18" s="87" t="n"/>
+      <c r="F18" s="86" t="n"/>
+      <c r="G18" s="87" t="n"/>
+      <c r="H18" s="87" t="n"/>
+      <c r="I18" s="84" t="n"/>
+      <c r="J18" s="86" t="n"/>
+      <c r="K18" s="87" t="n"/>
+      <c r="L18" s="87" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1" s="33">
-      <c r="A19" s="48" t="n">
+      <c r="A19" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="46" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="48" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="48" t="n"/>
-      <c r="H19" s="48" t="n"/>
-      <c r="I19" s="46" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="48" t="n"/>
-      <c r="L19" s="48" t="n"/>
+      <c r="B19" s="84" t="n"/>
+      <c r="C19" s="85" t="n"/>
+      <c r="D19" s="86" t="n"/>
+      <c r="E19" s="87" t="n"/>
+      <c r="F19" s="86" t="n"/>
+      <c r="G19" s="87" t="n"/>
+      <c r="H19" s="87" t="n"/>
+      <c r="I19" s="84" t="n"/>
+      <c r="J19" s="86" t="n"/>
+      <c r="K19" s="87" t="n"/>
+      <c r="L19" s="87" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1" s="33">
-      <c r="A20" s="48" t="n">
+      <c r="A20" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="46" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="48" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="48" t="n"/>
-      <c r="H20" s="48" t="n"/>
-      <c r="I20" s="46" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="48" t="n"/>
-      <c r="L20" s="48" t="n"/>
+      <c r="B20" s="84" t="n"/>
+      <c r="C20" s="85" t="n"/>
+      <c r="D20" s="86" t="n"/>
+      <c r="E20" s="87" t="n"/>
+      <c r="F20" s="86" t="n"/>
+      <c r="G20" s="87" t="n"/>
+      <c r="H20" s="87" t="n"/>
+      <c r="I20" s="84" t="n"/>
+      <c r="J20" s="86" t="n"/>
+      <c r="K20" s="87" t="n"/>
+      <c r="L20" s="87" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1" s="33">
-      <c r="A21" s="48" t="n">
+      <c r="A21" s="83" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="48" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="48" t="n"/>
-      <c r="H21" s="48" t="n"/>
-      <c r="I21" s="46" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="48" t="n"/>
-      <c r="L21" s="48" t="n"/>
+      <c r="B21" s="84" t="n"/>
+      <c r="C21" s="85" t="n"/>
+      <c r="D21" s="86" t="n"/>
+      <c r="E21" s="87" t="n"/>
+      <c r="F21" s="86" t="n"/>
+      <c r="G21" s="87" t="n"/>
+      <c r="H21" s="87" t="n"/>
+      <c r="I21" s="84" t="n"/>
+      <c r="J21" s="86" t="n"/>
+      <c r="K21" s="87" t="n"/>
+      <c r="L21" s="87" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1" s="33">
-      <c r="A22" s="48" t="n">
+      <c r="A22" s="83" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="46" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="48" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="48" t="n"/>
-      <c r="H22" s="48" t="n"/>
-      <c r="I22" s="46" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="48" t="n"/>
-      <c r="L22" s="48" t="n"/>
+      <c r="B22" s="84" t="n"/>
+      <c r="C22" s="85" t="n"/>
+      <c r="D22" s="86" t="n"/>
+      <c r="E22" s="87" t="n"/>
+      <c r="F22" s="86" t="n"/>
+      <c r="G22" s="87" t="n"/>
+      <c r="H22" s="87" t="n"/>
+      <c r="I22" s="84" t="n"/>
+      <c r="J22" s="86" t="n"/>
+      <c r="K22" s="87" t="n"/>
+      <c r="L22" s="87" t="n"/>
     </row>
     <row r="23" ht="22.05" customHeight="1" s="33">
-      <c r="A23" s="48" t="n">
+      <c r="A23" s="83" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="46" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="48" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="48" t="n"/>
-      <c r="H23" s="48" t="n"/>
-      <c r="I23" s="46" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="48" t="n"/>
-      <c r="L23" s="48" t="n"/>
+      <c r="B23" s="84" t="n"/>
+      <c r="C23" s="85" t="n"/>
+      <c r="D23" s="86" t="n"/>
+      <c r="E23" s="87" t="n"/>
+      <c r="F23" s="86" t="n"/>
+      <c r="G23" s="87" t="n"/>
+      <c r="H23" s="87" t="n"/>
+      <c r="I23" s="84" t="n"/>
+      <c r="J23" s="86" t="n"/>
+      <c r="K23" s="87" t="n"/>
+      <c r="L23" s="87" t="n"/>
     </row>
     <row r="24" ht="22.05" customHeight="1" s="33">
-      <c r="A24" s="48" t="n">
+      <c r="A24" s="83" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="46" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="48" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="48" t="n"/>
-      <c r="H24" s="48" t="n"/>
-      <c r="I24" s="46" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="48" t="n"/>
-      <c r="L24" s="48" t="n"/>
+      <c r="B24" s="84" t="n"/>
+      <c r="C24" s="85" t="n"/>
+      <c r="D24" s="86" t="n"/>
+      <c r="E24" s="87" t="n"/>
+      <c r="F24" s="86" t="n"/>
+      <c r="G24" s="87" t="n"/>
+      <c r="H24" s="87" t="n"/>
+      <c r="I24" s="84" t="n"/>
+      <c r="J24" s="86" t="n"/>
+      <c r="K24" s="87" t="n"/>
+      <c r="L24" s="87" t="n"/>
     </row>
     <row r="25" ht="22.05" customHeight="1" s="33">
-      <c r="A25" s="48" t="n">
+      <c r="A25" s="83" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="46" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="48" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="48" t="n"/>
-      <c r="H25" s="48" t="n"/>
-      <c r="I25" s="46" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="48" t="n"/>
-      <c r="L25" s="48" t="n"/>
+      <c r="B25" s="84" t="n"/>
+      <c r="C25" s="85" t="n"/>
+      <c r="D25" s="86" t="n"/>
+      <c r="E25" s="87" t="n"/>
+      <c r="F25" s="86" t="n"/>
+      <c r="G25" s="87" t="n"/>
+      <c r="H25" s="87" t="n"/>
+      <c r="I25" s="84" t="n"/>
+      <c r="J25" s="86" t="n"/>
+      <c r="K25" s="87" t="n"/>
+      <c r="L25" s="87" t="n"/>
     </row>
     <row r="26" ht="22.05" customHeight="1" s="33">
-      <c r="A26" s="48" t="n">
+      <c r="A26" s="83" t="n">
         <v>11</v>
       </c>
-      <c r="B26" s="46" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="48" t="n"/>
-      <c r="F26" s="20" t="n"/>
-      <c r="G26" s="48" t="n"/>
-      <c r="H26" s="48" t="n"/>
-      <c r="I26" s="46" t="n"/>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="48" t="n"/>
-      <c r="L26" s="48" t="n"/>
+      <c r="B26" s="84" t="n"/>
+      <c r="C26" s="85" t="n"/>
+      <c r="D26" s="86" t="n"/>
+      <c r="E26" s="87" t="n"/>
+      <c r="F26" s="86" t="n"/>
+      <c r="G26" s="87" t="n"/>
+      <c r="H26" s="87" t="n"/>
+      <c r="I26" s="84" t="n"/>
+      <c r="J26" s="86" t="n"/>
+      <c r="K26" s="87" t="n"/>
+      <c r="L26" s="87" t="n"/>
     </row>
     <row r="27" ht="22.05" customHeight="1" s="33">
-      <c r="A27" s="48" t="n">
+      <c r="A27" s="83" t="n">
         <v>12</v>
       </c>
-      <c r="B27" s="46" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="48" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="48" t="n"/>
-      <c r="H27" s="48" t="n"/>
-      <c r="I27" s="46" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="48" t="n"/>
-      <c r="L27" s="48" t="n"/>
+      <c r="B27" s="84" t="n"/>
+      <c r="C27" s="85" t="n"/>
+      <c r="D27" s="86" t="n"/>
+      <c r="E27" s="87" t="n"/>
+      <c r="F27" s="86" t="n"/>
+      <c r="G27" s="87" t="n"/>
+      <c r="H27" s="87" t="n"/>
+      <c r="I27" s="84" t="n"/>
+      <c r="J27" s="86" t="n"/>
+      <c r="K27" s="87" t="n"/>
+      <c r="L27" s="87" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="33">
       <c r="A28" s="35" t="inlineStr">
@@ -3223,10 +3339,10 @@
       <c r="L29" s="28" t="n"/>
     </row>
     <row r="30" ht="16.95" customHeight="1" s="33">
-      <c r="A30" s="48" t="n">
+      <c r="A30" s="83" t="n">
         <v>1</v>
       </c>
-      <c r="B30" s="46" t="inlineStr">
+      <c r="B30" s="88" t="inlineStr">
         <is>
           <t>Zona de almacenamiento señalizada, ventilada y techada</t>
         </is>
@@ -3237,16 +3353,16 @@
       <c r="F30" s="24" t="n"/>
       <c r="G30" s="24" t="n"/>
       <c r="H30" s="20" t="n"/>
-      <c r="I30" s="48" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="47" t="n"/>
-      <c r="L30" s="20" t="n"/>
+      <c r="I30" s="87" t="n"/>
+      <c r="J30" s="86" t="n"/>
+      <c r="K30" s="84" t="n"/>
+      <c r="L30" s="86" t="n"/>
     </row>
     <row r="31" ht="16.95" customHeight="1" s="33">
-      <c r="A31" s="48" t="n">
+      <c r="A31" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="B31" s="46" t="inlineStr">
+      <c r="B31" s="88" t="inlineStr">
         <is>
           <t>Piso impermeable con contención o dique para el 110 % del recipiente mayor</t>
         </is>
@@ -3257,16 +3373,16 @@
       <c r="F31" s="24" t="n"/>
       <c r="G31" s="24" t="n"/>
       <c r="H31" s="20" t="n"/>
-      <c r="I31" s="48" t="n"/>
-      <c r="J31" s="20" t="n"/>
-      <c r="K31" s="47" t="n"/>
-      <c r="L31" s="20" t="n"/>
+      <c r="I31" s="87" t="n"/>
+      <c r="J31" s="86" t="n"/>
+      <c r="K31" s="84" t="n"/>
+      <c r="L31" s="86" t="n"/>
     </row>
     <row r="32" ht="16.95" customHeight="1" s="33">
-      <c r="A32" s="48" t="n">
+      <c r="A32" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="B32" s="46" t="inlineStr">
+      <c r="B32" s="88" t="inlineStr">
         <is>
           <t>Recipientes cerrados, rotulados y en buen estado</t>
         </is>
@@ -3277,16 +3393,16 @@
       <c r="F32" s="24" t="n"/>
       <c r="G32" s="24" t="n"/>
       <c r="H32" s="20" t="n"/>
-      <c r="I32" s="48" t="n"/>
-      <c r="J32" s="20" t="n"/>
-      <c r="K32" s="47" t="n"/>
-      <c r="L32" s="20" t="n"/>
+      <c r="I32" s="87" t="n"/>
+      <c r="J32" s="86" t="n"/>
+      <c r="K32" s="84" t="n"/>
+      <c r="L32" s="86" t="n"/>
     </row>
     <row r="33" ht="16.95" customHeight="1" s="33">
-      <c r="A33" s="48" t="n">
+      <c r="A33" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="B33" s="46" t="inlineStr">
+      <c r="B33" s="88" t="inlineStr">
         <is>
           <t>Hojas de seguridad (SDS) impresas y visibles en el sitio</t>
         </is>
@@ -3297,16 +3413,16 @@
       <c r="F33" s="24" t="n"/>
       <c r="G33" s="24" t="n"/>
       <c r="H33" s="20" t="n"/>
-      <c r="I33" s="48" t="n"/>
-      <c r="J33" s="20" t="n"/>
-      <c r="K33" s="47" t="n"/>
-      <c r="L33" s="20" t="n"/>
+      <c r="I33" s="87" t="n"/>
+      <c r="J33" s="86" t="n"/>
+      <c r="K33" s="84" t="n"/>
+      <c r="L33" s="86" t="n"/>
     </row>
     <row r="34" ht="16.95" customHeight="1" s="33">
-      <c r="A34" s="48" t="n">
+      <c r="A34" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="B34" s="46" t="inlineStr">
+      <c r="B34" s="88" t="inlineStr">
         <is>
           <t>Sustancias incompatibles almacenadas por separado</t>
         </is>
@@ -3317,16 +3433,16 @@
       <c r="F34" s="24" t="n"/>
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="20" t="n"/>
-      <c r="I34" s="48" t="n"/>
-      <c r="J34" s="20" t="n"/>
-      <c r="K34" s="47" t="n"/>
-      <c r="L34" s="20" t="n"/>
+      <c r="I34" s="87" t="n"/>
+      <c r="J34" s="86" t="n"/>
+      <c r="K34" s="84" t="n"/>
+      <c r="L34" s="86" t="n"/>
     </row>
     <row r="35" ht="16.95" customHeight="1" s="33">
-      <c r="A35" s="48" t="n">
+      <c r="A35" s="83" t="n">
         <v>6</v>
       </c>
-      <c r="B35" s="46" t="inlineStr">
+      <c r="B35" s="88" t="inlineStr">
         <is>
           <t>Kit antiderrames disponible y completo</t>
         </is>
@@ -3337,16 +3453,16 @@
       <c r="F35" s="24" t="n"/>
       <c r="G35" s="24" t="n"/>
       <c r="H35" s="20" t="n"/>
-      <c r="I35" s="48" t="n"/>
-      <c r="J35" s="20" t="n"/>
-      <c r="K35" s="47" t="n"/>
-      <c r="L35" s="20" t="n"/>
+      <c r="I35" s="87" t="n"/>
+      <c r="J35" s="86" t="n"/>
+      <c r="K35" s="84" t="n"/>
+      <c r="L35" s="86" t="n"/>
     </row>
     <row r="36" ht="16.95" customHeight="1" s="33">
-      <c r="A36" s="48" t="n">
+      <c r="A36" s="83" t="n">
         <v>7</v>
       </c>
-      <c r="B36" s="46" t="inlineStr">
+      <c r="B36" s="88" t="inlineStr">
         <is>
           <t>Extintor adecuado y vigente cerca de la zona</t>
         </is>
@@ -3357,16 +3473,16 @@
       <c r="F36" s="24" t="n"/>
       <c r="G36" s="24" t="n"/>
       <c r="H36" s="20" t="n"/>
-      <c r="I36" s="48" t="n"/>
-      <c r="J36" s="20" t="n"/>
-      <c r="K36" s="47" t="n"/>
-      <c r="L36" s="20" t="n"/>
+      <c r="I36" s="87" t="n"/>
+      <c r="J36" s="86" t="n"/>
+      <c r="K36" s="84" t="n"/>
+      <c r="L36" s="86" t="n"/>
     </row>
     <row r="37" ht="16.95" customHeight="1" s="33">
-      <c r="A37" s="48" t="n">
+      <c r="A37" s="83" t="n">
         <v>8</v>
       </c>
-      <c r="B37" s="46" t="inlineStr">
+      <c r="B37" s="88" t="inlineStr">
         <is>
           <t>Prohibición de fumar y fuentes de ignición señalizadas</t>
         </is>
@@ -3377,16 +3493,16 @@
       <c r="F37" s="24" t="n"/>
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="20" t="n"/>
-      <c r="I37" s="48" t="n"/>
-      <c r="J37" s="20" t="n"/>
-      <c r="K37" s="47" t="n"/>
-      <c r="L37" s="20" t="n"/>
+      <c r="I37" s="87" t="n"/>
+      <c r="J37" s="86" t="n"/>
+      <c r="K37" s="84" t="n"/>
+      <c r="L37" s="86" t="n"/>
     </row>
     <row r="38" ht="16.95" customHeight="1" s="33">
-      <c r="A38" s="48" t="n">
+      <c r="A38" s="83" t="n">
         <v>9</v>
       </c>
-      <c r="B38" s="46" t="inlineStr">
+      <c r="B38" s="88" t="inlineStr">
         <is>
           <t>Personal capacitado en manejo de sustancias y con EPP disponible</t>
         </is>
@@ -3397,16 +3513,16 @@
       <c r="F38" s="24" t="n"/>
       <c r="G38" s="24" t="n"/>
       <c r="H38" s="20" t="n"/>
-      <c r="I38" s="48" t="n"/>
-      <c r="J38" s="20" t="n"/>
-      <c r="K38" s="47" t="n"/>
-      <c r="L38" s="20" t="n"/>
+      <c r="I38" s="87" t="n"/>
+      <c r="J38" s="86" t="n"/>
+      <c r="K38" s="84" t="n"/>
+      <c r="L38" s="86" t="n"/>
     </row>
     <row r="39" ht="16.95" customHeight="1" s="33">
-      <c r="A39" s="48" t="n">
+      <c r="A39" s="83" t="n">
         <v>10</v>
       </c>
-      <c r="B39" s="46" t="inlineStr">
+      <c r="B39" s="88" t="inlineStr">
         <is>
           <t>Sin derrames, goteos ni manchas en la zona</t>
         </is>
@@ -3417,16 +3533,16 @@
       <c r="F39" s="24" t="n"/>
       <c r="G39" s="24" t="n"/>
       <c r="H39" s="20" t="n"/>
-      <c r="I39" s="48" t="n"/>
-      <c r="J39" s="20" t="n"/>
-      <c r="K39" s="47" t="n"/>
-      <c r="L39" s="20" t="n"/>
+      <c r="I39" s="87" t="n"/>
+      <c r="J39" s="86" t="n"/>
+      <c r="K39" s="84" t="n"/>
+      <c r="L39" s="86" t="n"/>
     </row>
     <row r="40" ht="16.95" customHeight="1" s="33">
-      <c r="A40" s="48" t="n">
+      <c r="A40" s="83" t="n">
         <v>11</v>
       </c>
-      <c r="B40" s="46" t="inlineStr">
+      <c r="B40" s="88" t="inlineStr">
         <is>
           <t>Tanques de combustible con contención y conexión a tierra</t>
         </is>
@@ -3437,16 +3553,16 @@
       <c r="F40" s="24" t="n"/>
       <c r="G40" s="24" t="n"/>
       <c r="H40" s="20" t="n"/>
-      <c r="I40" s="48" t="n"/>
-      <c r="J40" s="20" t="n"/>
-      <c r="K40" s="47" t="n"/>
-      <c r="L40" s="20" t="n"/>
+      <c r="I40" s="87" t="n"/>
+      <c r="J40" s="86" t="n"/>
+      <c r="K40" s="84" t="n"/>
+      <c r="L40" s="86" t="n"/>
     </row>
     <row r="41" ht="16.95" customHeight="1" s="33">
-      <c r="A41" s="48" t="n">
+      <c r="A41" s="83" t="n">
         <v>12</v>
       </c>
-      <c r="B41" s="46" t="inlineStr">
+      <c r="B41" s="88" t="inlineStr">
         <is>
           <t>Registro de entradas y salidas actualizado</t>
         </is>
@@ -3457,16 +3573,16 @@
       <c r="F41" s="24" t="n"/>
       <c r="G41" s="24" t="n"/>
       <c r="H41" s="20" t="n"/>
-      <c r="I41" s="48" t="n"/>
-      <c r="J41" s="20" t="n"/>
-      <c r="K41" s="47" t="n"/>
-      <c r="L41" s="20" t="n"/>
+      <c r="I41" s="87" t="n"/>
+      <c r="J41" s="86" t="n"/>
+      <c r="K41" s="84" t="n"/>
+      <c r="L41" s="86" t="n"/>
     </row>
     <row r="42" ht="16.95" customHeight="1" s="33">
-      <c r="A42" s="48" t="n">
+      <c r="A42" s="83" t="n">
         <v>13</v>
       </c>
-      <c r="B42" s="46" t="inlineStr">
+      <c r="B42" s="88" t="inlineStr">
         <is>
           <t>Envases vacíos manejados como residuo peligroso</t>
         </is>
@@ -3477,10 +3593,10 @@
       <c r="F42" s="24" t="n"/>
       <c r="G42" s="24" t="n"/>
       <c r="H42" s="20" t="n"/>
-      <c r="I42" s="48" t="n"/>
-      <c r="J42" s="20" t="n"/>
-      <c r="K42" s="47" t="n"/>
-      <c r="L42" s="20" t="n"/>
+      <c r="I42" s="87" t="n"/>
+      <c r="J42" s="86" t="n"/>
+      <c r="K42" s="84" t="n"/>
+      <c r="L42" s="86" t="n"/>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="33">
       <c r="A43" s="35" t="inlineStr">
@@ -3535,68 +3651,68 @@
       </c>
     </row>
     <row r="45" ht="24" customHeight="1" s="33">
-      <c r="A45" s="48" t="n">
+      <c r="A45" s="83" t="n">
         <v>1</v>
       </c>
-      <c r="B45" s="46" t="n"/>
-      <c r="C45" s="24" t="n"/>
-      <c r="D45" s="24" t="n"/>
-      <c r="E45" s="24" t="n"/>
-      <c r="F45" s="20" t="n"/>
-      <c r="G45" s="46" t="n"/>
-      <c r="H45" s="24" t="n"/>
-      <c r="I45" s="20" t="n"/>
-      <c r="J45" s="46" t="n"/>
-      <c r="K45" s="20" t="n"/>
-      <c r="L45" s="52" t="n"/>
+      <c r="B45" s="84" t="n"/>
+      <c r="C45" s="85" t="n"/>
+      <c r="D45" s="85" t="n"/>
+      <c r="E45" s="85" t="n"/>
+      <c r="F45" s="86" t="n"/>
+      <c r="G45" s="84" t="n"/>
+      <c r="H45" s="85" t="n"/>
+      <c r="I45" s="86" t="n"/>
+      <c r="J45" s="84" t="n"/>
+      <c r="K45" s="86" t="n"/>
+      <c r="L45" s="89" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1" s="33">
-      <c r="A46" s="48" t="n">
+      <c r="A46" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="B46" s="46" t="n"/>
-      <c r="C46" s="24" t="n"/>
-      <c r="D46" s="24" t="n"/>
-      <c r="E46" s="24" t="n"/>
-      <c r="F46" s="20" t="n"/>
-      <c r="G46" s="46" t="n"/>
-      <c r="H46" s="24" t="n"/>
-      <c r="I46" s="20" t="n"/>
-      <c r="J46" s="46" t="n"/>
-      <c r="K46" s="20" t="n"/>
-      <c r="L46" s="52" t="n"/>
+      <c r="B46" s="84" t="n"/>
+      <c r="C46" s="85" t="n"/>
+      <c r="D46" s="85" t="n"/>
+      <c r="E46" s="85" t="n"/>
+      <c r="F46" s="86" t="n"/>
+      <c r="G46" s="84" t="n"/>
+      <c r="H46" s="85" t="n"/>
+      <c r="I46" s="86" t="n"/>
+      <c r="J46" s="84" t="n"/>
+      <c r="K46" s="86" t="n"/>
+      <c r="L46" s="89" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1" s="33">
-      <c r="A47" s="48" t="n">
+      <c r="A47" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="B47" s="46" t="n"/>
-      <c r="C47" s="24" t="n"/>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="20" t="n"/>
-      <c r="G47" s="46" t="n"/>
-      <c r="H47" s="24" t="n"/>
-      <c r="I47" s="20" t="n"/>
-      <c r="J47" s="46" t="n"/>
-      <c r="K47" s="20" t="n"/>
-      <c r="L47" s="52" t="n"/>
+      <c r="B47" s="84" t="n"/>
+      <c r="C47" s="85" t="n"/>
+      <c r="D47" s="85" t="n"/>
+      <c r="E47" s="85" t="n"/>
+      <c r="F47" s="86" t="n"/>
+      <c r="G47" s="84" t="n"/>
+      <c r="H47" s="85" t="n"/>
+      <c r="I47" s="86" t="n"/>
+      <c r="J47" s="84" t="n"/>
+      <c r="K47" s="86" t="n"/>
+      <c r="L47" s="89" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1" s="33">
-      <c r="A48" s="48" t="n">
+      <c r="A48" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="B48" s="46" t="n"/>
-      <c r="C48" s="24" t="n"/>
-      <c r="D48" s="24" t="n"/>
-      <c r="E48" s="24" t="n"/>
-      <c r="F48" s="20" t="n"/>
-      <c r="G48" s="46" t="n"/>
-      <c r="H48" s="24" t="n"/>
-      <c r="I48" s="20" t="n"/>
-      <c r="J48" s="46" t="n"/>
-      <c r="K48" s="20" t="n"/>
-      <c r="L48" s="52" t="n"/>
+      <c r="B48" s="84" t="n"/>
+      <c r="C48" s="85" t="n"/>
+      <c r="D48" s="85" t="n"/>
+      <c r="E48" s="85" t="n"/>
+      <c r="F48" s="86" t="n"/>
+      <c r="G48" s="84" t="n"/>
+      <c r="H48" s="85" t="n"/>
+      <c r="I48" s="86" t="n"/>
+      <c r="J48" s="84" t="n"/>
+      <c r="K48" s="86" t="n"/>
+      <c r="L48" s="89" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="33">
       <c r="A49" s="35" t="inlineStr">
@@ -3617,18 +3733,18 @@
       <c r="L49" s="20" t="n"/>
     </row>
     <row r="50" ht="43.95" customHeight="1" s="33">
-      <c r="A50" s="50" t="n"/>
-      <c r="B50" s="30" t="n"/>
-      <c r="C50" s="30" t="n"/>
-      <c r="D50" s="30" t="n"/>
-      <c r="E50" s="30" t="n"/>
-      <c r="F50" s="30" t="n"/>
-      <c r="G50" s="30" t="n"/>
-      <c r="H50" s="30" t="n"/>
-      <c r="I50" s="30" t="n"/>
-      <c r="J50" s="30" t="n"/>
-      <c r="K50" s="30" t="n"/>
-      <c r="L50" s="22" t="n"/>
+      <c r="A50" s="90" t="n"/>
+      <c r="B50" s="80" t="n"/>
+      <c r="C50" s="80" t="n"/>
+      <c r="D50" s="80" t="n"/>
+      <c r="E50" s="80" t="n"/>
+      <c r="F50" s="80" t="n"/>
+      <c r="G50" s="80" t="n"/>
+      <c r="H50" s="80" t="n"/>
+      <c r="I50" s="80" t="n"/>
+      <c r="J50" s="80" t="n"/>
+      <c r="K50" s="80" t="n"/>
+      <c r="L50" s="81" t="n"/>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="33">
       <c r="A51" s="35" t="inlineStr">
@@ -3677,20 +3793,20 @@
         </is>
       </c>
       <c r="B53" s="20" t="n"/>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="24" t="n"/>
-      <c r="E53" s="24" t="n"/>
-      <c r="F53" s="20" t="n"/>
+      <c r="C53" s="84" t="n"/>
+      <c r="D53" s="85" t="n"/>
+      <c r="E53" s="85" t="n"/>
+      <c r="F53" s="86" t="n"/>
       <c r="G53" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="H53" s="20" t="n"/>
-      <c r="I53" s="23" t="n"/>
-      <c r="J53" s="24" t="n"/>
-      <c r="K53" s="24" t="n"/>
-      <c r="L53" s="20" t="n"/>
+      <c r="I53" s="84" t="n"/>
+      <c r="J53" s="85" t="n"/>
+      <c r="K53" s="85" t="n"/>
+      <c r="L53" s="86" t="n"/>
     </row>
     <row r="54" ht="21" customHeight="1" s="33">
       <c r="A54" s="19" t="inlineStr">
@@ -3699,20 +3815,20 @@
         </is>
       </c>
       <c r="B54" s="20" t="n"/>
-      <c r="C54" s="23" t="n"/>
-      <c r="D54" s="24" t="n"/>
-      <c r="E54" s="24" t="n"/>
-      <c r="F54" s="20" t="n"/>
+      <c r="C54" s="84" t="n"/>
+      <c r="D54" s="85" t="n"/>
+      <c r="E54" s="85" t="n"/>
+      <c r="F54" s="86" t="n"/>
       <c r="G54" s="19" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="H54" s="20" t="n"/>
-      <c r="I54" s="23" t="n"/>
-      <c r="J54" s="24" t="n"/>
-      <c r="K54" s="24" t="n"/>
-      <c r="L54" s="20" t="n"/>
+      <c r="I54" s="84" t="n"/>
+      <c r="J54" s="85" t="n"/>
+      <c r="K54" s="85" t="n"/>
+      <c r="L54" s="86" t="n"/>
     </row>
     <row r="55" ht="21" customHeight="1" s="33">
       <c r="A55" s="19" t="inlineStr">
@@ -3721,20 +3837,20 @@
         </is>
       </c>
       <c r="B55" s="20" t="n"/>
-      <c r="C55" s="23" t="n"/>
-      <c r="D55" s="24" t="n"/>
-      <c r="E55" s="24" t="n"/>
-      <c r="F55" s="20" t="n"/>
+      <c r="C55" s="84" t="n"/>
+      <c r="D55" s="85" t="n"/>
+      <c r="E55" s="85" t="n"/>
+      <c r="F55" s="86" t="n"/>
       <c r="G55" s="19" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="H55" s="20" t="n"/>
-      <c r="I55" s="23" t="n"/>
-      <c r="J55" s="24" t="n"/>
-      <c r="K55" s="24" t="n"/>
-      <c r="L55" s="20" t="n"/>
+      <c r="I55" s="84" t="n"/>
+      <c r="J55" s="85" t="n"/>
+      <c r="K55" s="85" t="n"/>
+      <c r="L55" s="86" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3748,6 +3864,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="140">
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="K33:L33"/>
